--- a/tests/fixtures/INFO.xlsx
+++ b/tests/fixtures/INFO.xlsx
@@ -653,7 +653,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ΜΑΚΕΔΟΝΙΑ</t>
+          <t>ΜΑΚΕΔΟΝΙΑ ΘΕΣΣΑΛΟΝΙΚΗ ΠΕΡΙΟΧΗ ΤΕΣΤ ΜΑΚΡΥ</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ΜΕΤΑΦ Β</t>
+          <t>ΜΕΤΑΦΟΡΙΚΗ ΑΦΟΙ ΠΑΠΑΣ</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
